--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_ALTO_MONTO.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_ALTO_MONTO.xlsx
@@ -2319,11 +2319,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="2793448"/>
-        <c:axId val="66524442"/>
+        <c:axId val="96973080"/>
+        <c:axId val="59470166"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="2793448"/>
+        <c:axId val="96973080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2357,7 +2357,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66524442"/>
+        <c:crossAx val="59470166"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2369,7 +2369,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="66524442"/>
+        <c:axId val="59470166"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2412,7 +2412,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2793448"/>
+        <c:crossAx val="96973080"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2961,7 +2961,7 @@
                   <c:v>102.156233333719</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>76.171481911528</c:v>
+                  <c:v>77.2635458001809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2976,11 +2976,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="50904043"/>
-        <c:axId val="74430782"/>
+        <c:axId val="3355742"/>
+        <c:axId val="27355565"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="50904043"/>
+        <c:axId val="3355742"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3012,14 +3012,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74430782"/>
+        <c:crossAx val="27355565"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="74430782"/>
+        <c:axId val="27355565"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3093,7 +3093,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50904043"/>
+        <c:crossAx val="3355742"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="AW20" s="34" t="n">
         <f aca="false">LOOKUP(AW19,$A$3:$A$2976,$B$3:$B$2976)</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="AX20" s="34" t="n">
         <f aca="false">LOOKUP(AX19,$A$3:$A$2976,$B$3:$B$2976)</f>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AH22" s="23" t="n">
         <f aca="false">+S23/R23-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI22" s="9"/>
       <c r="AJ22" s="9"/>
@@ -7093,7 +7093,7 @@
       <c r="AP22" s="9"/>
       <c r="AQ22" s="24" t="n">
         <f aca="false">+(S23/P23-1)/COUNTA(AE22:AP22)*12</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="AV22" s="29" t="s">
         <v>19</v>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="S23" s="3" t="n">
         <f aca="false">+B252</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="U23" s="20"/>
       <c r="Y23" s="20"/>
@@ -7644,23 +7644,23 @@
       </c>
       <c r="AX29" s="42" t="n">
         <f aca="false">$AW20/AX20-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AY29" s="42" t="n">
         <f aca="false">$AW20/AY20-1</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="AZ29" s="42" t="n">
         <f aca="false">$AW20/AZ20-1</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="BA29" s="42" t="n">
         <f aca="false">$AW20/BA20-1</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="BB29" s="42" t="n">
         <f aca="false">+AQ86</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="BC29" s="43"/>
       <c r="BD29" s="28"/>
@@ -11182,7 +11182,7 @@
       </c>
       <c r="AH86" s="60" t="n">
         <f aca="false">+AH22</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI86" s="60"/>
       <c r="AJ86" s="60"/>
@@ -11194,7 +11194,7 @@
       <c r="AP86" s="60"/>
       <c r="AQ86" s="60" t="n">
         <f aca="false">+AQ22</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="87" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15353,15 +15353,15 @@
         <v>46142</v>
       </c>
       <c r="B252" s="3" t="n">
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="C252" s="26" t="n">
         <f aca="false">(B252/B251-1)/(A252-A251)*30/1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="D252" s="20" t="n">
         <f aca="false">+D251*(1+C252)</f>
-        <v>76.171481911528</v>
+        <v>77.2635458001809</v>
       </c>
       <c r="F252" s="18" t="n">
         <v>46142</v>
@@ -15490,15 +15490,15 @@
       </c>
       <c r="T2" s="83" t="n">
         <f aca="false">+'Datos ICP (2)'!AX29</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="U2" s="83" t="n">
         <f aca="false">+'Datos ICP (2)'!AY29</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="V2" s="83" t="n">
         <f aca="false">+'Datos ICP (2)'!AZ29</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="W2" s="83" t="n">
         <f aca="false">+Q33</f>
@@ -15506,7 +15506,7 @@
       </c>
       <c r="X2" s="83" t="n">
         <f aca="false">+'Datos ICP (2)'!BB29</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16649,7 +16649,7 @@
       </c>
       <c r="H39" s="90" t="n">
         <f aca="false">+'Datos ICP (2)'!AH86</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_ALTO_MONTO.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_ALTO_MONTO.xlsx
@@ -2319,11 +2319,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="96973080"/>
-        <c:axId val="59470166"/>
+        <c:axId val="97474667"/>
+        <c:axId val="61250460"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="96973080"/>
+        <c:axId val="97474667"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2357,7 +2357,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59470166"/>
+        <c:crossAx val="61250460"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2369,7 +2369,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="59470166"/>
+        <c:axId val="61250460"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2412,7 +2412,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96973080"/>
+        <c:crossAx val="97474667"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2976,11 +2976,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="3355742"/>
-        <c:axId val="27355565"/>
+        <c:axId val="59003482"/>
+        <c:axId val="13480677"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="3355742"/>
+        <c:axId val="59003482"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3012,14 +3012,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27355565"/>
+        <c:crossAx val="13480677"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="27355565"/>
+        <c:axId val="13480677"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3093,7 +3093,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="3355742"/>
+        <c:crossAx val="59003482"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_ALTO_MONTO.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_ALTO_MONTO.xlsx
@@ -2319,11 +2319,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="97474667"/>
-        <c:axId val="61250460"/>
+        <c:axId val="36273782"/>
+        <c:axId val="72026835"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="97474667"/>
+        <c:axId val="36273782"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2357,7 +2357,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61250460"/>
+        <c:crossAx val="72026835"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2369,7 +2369,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="61250460"/>
+        <c:axId val="72026835"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2412,7 +2412,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97474667"/>
+        <c:crossAx val="36273782"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2976,11 +2976,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="59003482"/>
-        <c:axId val="13480677"/>
+        <c:axId val="20227954"/>
+        <c:axId val="69868231"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="59003482"/>
+        <c:axId val="20227954"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3012,14 +3012,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13480677"/>
+        <c:crossAx val="69868231"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="13480677"/>
+        <c:axId val="69868231"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3093,7 +3093,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59003482"/>
+        <c:crossAx val="20227954"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_ALTO_MONTO.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_ALTO_MONTO.xlsx
@@ -2319,11 +2319,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="36273782"/>
-        <c:axId val="72026835"/>
+        <c:axId val="91676617"/>
+        <c:axId val="45415049"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="36273782"/>
+        <c:axId val="91676617"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2357,7 +2357,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72026835"/>
+        <c:crossAx val="45415049"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2369,7 +2369,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="72026835"/>
+        <c:axId val="45415049"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2412,7 +2412,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36273782"/>
+        <c:crossAx val="91676617"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2976,11 +2976,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="20227954"/>
-        <c:axId val="69868231"/>
+        <c:axId val="67503518"/>
+        <c:axId val="358872"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="20227954"/>
+        <c:axId val="67503518"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3012,14 +3012,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69868231"/>
+        <c:crossAx val="358872"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="69868231"/>
+        <c:axId val="358872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3093,7 +3093,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20227954"/>
+        <c:crossAx val="67503518"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
